--- a/docs/export-templates/AI问书_全域主控台数据导出.xlsx
+++ b/docs/export-templates/AI问书_全域主控台数据导出.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="64">
   <si>
     <t>平台主控台 · 实时总览</t>
   </si>
@@ -77,10 +77,34 @@
     <t>历史累计含追问</t>
   </si>
   <si>
+    <t>知识产品 KP 总数</t>
+  </si>
+  <si>
+    <t>个</t>
+  </si>
+  <si>
+    <t>含草稿与已下架（已发布 402 · 草稿 41 · 已下架 25）</t>
+  </si>
+  <si>
+    <t>知识库文件总数</t>
+  </si>
+  <si>
+    <t>不含已删除（文档 82000 · 图片 26000 · 音频 12000 · 视频 6000）</t>
+  </si>
+  <si>
+    <t>知识库存储总量</t>
+  </si>
+  <si>
+    <t>TB</t>
+  </si>
+  <si>
+    <t>原始文件合计，不含向量索引；媒体资源占 62%</t>
+  </si>
+  <si>
     <t>平台主控台 · 经营分析</t>
   </si>
   <si>
-    <t>导出时间：2026-07-14 10:00:00 · 统计区间：近 7 天（2026-07-09 ~ 2026-07-15） · 全平台 · 当前区间 07-09—07-15 · 对比 07-02—07-08</t>
+    <t>导出时间：2026-07-14 10:00:00 · 统计区间：近 7 天（2026-07-31 ~ 2026-08-06） · 全平台 · 当前区间 07-31—08-06 · 对比 07-24—07-30</t>
   </si>
   <si>
     <t>数据类型</t>
@@ -101,7 +125,7 @@
     <t>↑ +3.0%</t>
   </si>
   <si>
-    <t>区间精确去重</t>
+    <t>区间内按用户 ID 去重</t>
   </si>
   <si>
     <t>新增会员</t>
@@ -110,13 +134,40 @@
     <t>↑ +6.7%</t>
   </si>
   <si>
+    <t>历史首次开通，按用户 ID 去重；续费/回流不计入</t>
+  </si>
+  <si>
+    <t>续费率</t>
+  </si>
+  <si>
+    <t>43.9%</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>↑ +0.3%</t>
+  </si>
+  <si>
+    <t>到期完成续费 ÷ 到期会员</t>
+  </si>
+  <si>
+    <t>回流会员</t>
+  </si>
+  <si>
+    <t>↑ +6.0%</t>
+  </si>
+  <si>
+    <t>过期后重新开通，按用户 ID 去重；不算新增/续费</t>
+  </si>
+  <si>
     <t>区间 GMV</t>
   </si>
   <si>
     <t>↑ +5.2%</t>
   </si>
   <si>
-    <t>区间已支付</t>
+    <t>区间已支付（待支付/已失效不计入）</t>
   </si>
   <si>
     <t>区间提问数</t>
@@ -132,9 +183,6 @@
   </si>
   <si>
     <t>06-02</t>
-  </si>
-  <si>
-    <t>—</t>
   </si>
   <si>
     <t>自然日趋势</t>
@@ -628,7 +676,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -743,6 +791,48 @@
       </c>
       <c r="D9" s="6" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="8">
+        <v>468</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="5">
+        <v>126000</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="8">
+        <v>4.8</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -762,7 +852,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -775,7 +865,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -785,7 +875,7 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -805,10 +895,10 @@
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>4</v>
@@ -817,7 +907,7 @@
         <v>5</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>6</v>
@@ -825,10 +915,10 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C5" s="5">
         <v>124645</v>
@@ -837,18 +927,18 @@
         <v>11</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C6" s="8">
         <v>3108</v>
@@ -857,190 +947,230 @@
         <v>11</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="5">
-        <v>255920</v>
+        <v>41</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C8" s="8">
-        <v>812000</v>
+        <v>515</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C9" s="5">
-        <v>110595</v>
+        <v>255920</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C10" s="8">
-        <v>106226</v>
+        <v>812000</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>19</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="C11" s="5">
-        <v>108464</v>
+        <v>110595</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>19</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="C12" s="8">
-        <v>116000</v>
+        <v>106226</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>19</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C13" s="5">
-        <v>123536</v>
+        <v>108464</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>19</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="C14" s="8">
-        <v>125774</v>
+        <v>116000</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>19</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="C15" s="5">
-        <v>121405</v>
+        <v>123536</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>19</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>41</v>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="8">
+        <v>125774</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="5">
+        <v>121405</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
